--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -1,38 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27916"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B7C75DC-FB21-426B-AE9C-97E98F23D769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\divya\eclipse-workspace\Orange-HRM\TestData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>UserName</t>
   </si>
@@ -67,10 +54,7 @@
     <t>ADMIN@123</t>
   </si>
   <si>
-    <t>Admin@123</t>
-  </si>
-  <si>
-    <t>admin</t>
+    <t>Admin123</t>
   </si>
   <si>
     <t>Username</t>
@@ -79,17 +63,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="5">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -100,7 +77,12 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -114,7 +96,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -127,7 +108,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -139,21 +120,15 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -162,14 +137,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -178,10 +145,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -350,6 +317,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -376,24 +344,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -454,453 +423,428 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.39844" customWidth="1"/>
+    <col min="2" max="2" width="30.29688" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="21">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.75">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" ht="17.4">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" ht="18.75">
-      <c r="A3" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" ht="17.4">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" ht="18.75">
-      <c r="A4" s="1" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" ht="17.4">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.75">
-      <c r="A5" s="1" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" ht="17.4">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" ht="18.75">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" ht="18.75">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" ht="17.4">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" ht="17.4">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" ht="18.75">
-      <c r="A8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" ht="18.75">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" ht="17.4">
+      <c r="A8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" ht="17.4">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" ht="18.75">
-      <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" ht="17.4">
+      <c r="A10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" ht="18.75">
-      <c r="A11" s="1" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" ht="17.4">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" ht="18.75">
-      <c r="A12" s="1" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" ht="17.4">
+      <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" ht="18.75">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" ht="17.4">
       <c r="A13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" ht="18.75">
-      <c r="A14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" ht="18.75">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" ht="18.75">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" ht="18.75">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" ht="18.75">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" ht="18.75">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" ht="18.75">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" ht="18.75">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" ht="18.75">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" ht="18.75">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" ht="18.75">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" ht="18.75">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" ht="18.75">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" ht="18.75">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" ht="17.4">
+      <c r="A14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" ht="17.4">
+      <c r="A15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" ht="17.4">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" ht="17.4">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" ht="17.4">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" ht="17.4">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" ht="17.4">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" ht="17.4">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" ht="17.4">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" ht="17.4">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" ht="17.4">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" ht="17.4">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" ht="17.4">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" ht="17.4">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{664BCAF0-31E3-4EA7-87DC-CF8E6843F0BB}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="1" max="1" width="18.69922" customWidth="1"/>
+    <col min="2" max="2" width="15.59766" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1">
       <c r="A1" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" ht="17.4">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="17.4">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75">
-      <c r="A4" s="1" t="s">
+    <row r="4" ht="17.4">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -908,6 +852,5 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>ADMIN@123</t>
+  </si>
+  <si>
+    <t>admin</t>
   </si>
   <si>
     <t>Admin123</t>
@@ -601,10 +604,10 @@
     </row>
     <row r="12" ht="17.4">
       <c r="A12" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -620,7 +623,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -633,10 +636,10 @@
     </row>
     <row r="14" ht="17.4">
       <c r="A14" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -648,12 +651,7 @@
       <c r="J14" s="2"/>
     </row>
     <row r="15" ht="17.4">
-      <c r="A15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -821,7 +819,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
